--- a/data/qa/prospect_to_cash/pricing.xlsx
+++ b/data/qa/prospect_to_cash/pricing.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0015</t>
+          <t>KB-0103</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,43 +564,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>Pricing and Discount Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Order Entry</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Customer Orders</t>
-        </is>
-      </c>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>HELP_PROCESS</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>how_to</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>How is pricing determined on a Customer Order?</t>
+          <t>Where is pricing reviewed for customer orders and estimates?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pricing comes from the item's price list, any customer-specific pricing agreements, and applicable discounts — applied automatically when the item is added to an order line.</t>
+          <t>Pricing is determined for Estimate Lines and Customer Order Lines, with inputs that can include customer contracts, item pricing, customer/item price codes, promotions, quantity breaks, currency, and discounts. You should review the pricing source and effective date for the specific customer, item, and line.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>pricing,price list</t>
+          <t>pricing, estimate lines, customer order lines, price source, effective date</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -599,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>pricing.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Pricing and Discount Module &gt; Where pricing is reviewed</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -623,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -634,10 +640,598 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0104</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Can quoted, calculated, and invoiced prices differ?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Quoted price, current calculated price, and invoiced price may differ after revisions or timing changes.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>quoted price, calculated price, invoiced price, revisions, timing</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>pricing.md</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module &gt; Where pricing is reviewed</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0105</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>What is the price-check sequence for a line?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>To check the price for a line, confirm the customer, ship-to, site, item, U/M, currency, quantity, and due date. Review any customer contract or customer-item agreement and its effective dates, then review promotion pricing and item/customer price-code rules configured in the site. Check line and order discounts, surcharges, freight, and tax, and compare the calculated unit price with the approved quotation or customer purchase order. If the quantity or date changed, verify whether the system recalculated the price or retained the original, and resolve any discrepancy with the pricing owner before shipping or invoicing.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>price-check, discount, quantity, effective date, reprice</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>pricing.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module &gt; Price-check sequence for a line</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0106</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What should I check when moving an accepted estimate to an order?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>When moving an accepted estimate into an order, you should check every copied line, unit price, discount, freight, tax, currency, and total, as calculated amounts such as tax may be recalculated and some fields come from current customer or tax setup.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>estimate price, quote to order, copied order price, tax recalculation</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>pricing.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module &gt; Quote-to-order price handoff</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0107</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Is a copied order an exact financial snapshot of the quote?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>A copied order should not be represented as an exact financial snapshot of the quote without verification, since calculated amounts such as tax may be recalculated and some fields come from current customer or tax setup.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>quote to order, copied order price, estimate price</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>pricing.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module &gt; Quote-to-order price handoff</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0108</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>How can I find out the current price a customer gets today?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>To determine the current price a customer gets today, you must query approved SyteLine data using customer, item, quantity, date, site, and user permissions. Live customer-specific pricing requires an authorized, current ERP lookup.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>live price, customer-specific price, pricing permission, ERP lookup</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>pricing.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module &gt; Pricing permissions and current amounts</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0109</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Does this section show confidential contract prices or live unit-price results?</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>This section does not contain any customer's confidential contract price or live unit-price result.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>confidential contract price, live unit-price, pricing permission</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>pricing.md</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Pricing and Discount Module &gt; Pricing permissions and current amounts</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -654,39 +1248,669 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KB-0103</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>How do I review pricing for an order or estimate?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0103</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Where do I check the price used for a customer order?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0103</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>How is pricing reviewed in the system?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0104</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Do quoted and invoiced prices always match?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0104</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Can the price change between quote and invoice?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0104</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Is it possible for calculated and invoiced prices to be different?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0105</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>How do I check the price for a line?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0105</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>What steps are involved in verifying line pricing?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0105</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>How should I confirm the correct price for an order line?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0106</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What needs to be verified after copying an estimate to an order?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0106</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Do I need to review anything when converting a quote to an order?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0106</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What should I look for when transferring a quote to an order?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0107</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Will the order match the quote exactly after copying?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0107</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Is the copied order identical to the original quote?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0107</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Does copying a quote to an order keep all prices the same?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0108</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>How do I check a customer's live price?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0108</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What steps do I take to see today's price for a customer?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0108</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>How can I look up the current unit price for a customer?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KB-0109</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Are contract prices shown here?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KB-0109</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Is live pricing info included in this section?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KB-0109</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Does this section display actual customer prices?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
